--- a/Ecobliss_Results_new.xlsx
+++ b/Ecobliss_Results_new.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2025/Ghana_Project/QA1_&amp;_3/Documentation/ecobliss-docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE01D78-64AC-7244-AD95-796B69137356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCB564A-E7D2-294C-AD76-E2BF66FB0506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22860" yWindow="-9320" windowWidth="18500" windowHeight="18400" xr2:uid="{AA4B684E-F9E2-7F41-996C-BD2AB92E0EF7}"/>
+    <workbookView xWindow="-24860" yWindow="-9380" windowWidth="23420" windowHeight="15220" xr2:uid="{AA4B684E-F9E2-7F41-996C-BD2AB92E0EF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Net ERs" sheetId="1" r:id="rId1"/>
@@ -15025,7 +15025,7 @@
         <v>219</v>
       </c>
       <c r="B89" s="90" cm="1">
-        <f t="array" ref="B89">SQRT(AVERAGE((AN4:AN19)^2))</f>
+        <f t="array" ref="B89">SQRT(AVERAGE(('Project Model Error'!AN4:AN19)^2))</f>
         <v>3.4837523772744437E-14</v>
       </c>
       <c r="C89" s="58"/>
@@ -18265,7 +18265,7 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="D4" si="0">4.20750878</f>
+        <f>4.20750878</f>
         <v>4.2075087800000004</v>
       </c>
       <c r="E4">
@@ -18275,11 +18275,11 @@
         <v>4.1568867613368497E-2</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4" si="1">E4-D4</f>
+        <f t="shared" ref="G4" si="0">E4-D4</f>
         <v>29.534331220000002</v>
       </c>
       <c r="H4">
-        <f t="shared" ref="H4" si="2">(B4^2)/(C4*(C4-1))*G4^2</f>
+        <f t="shared" ref="H4" si="1">(B4^2)/(C4*(C4-1))*G4^2</f>
         <v>24624766.680670351</v>
       </c>
     </row>
